--- a/03_Outputs/Agroindustrial_Occidente/08_Educacion/educacion.xlsx
+++ b/03_Outputs/Agroindustrial_Occidente/08_Educacion/educacion.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="171" formatCode="0.0%"/>
     <numFmt numFmtId="172" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -37,23 +37,67 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -73,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -86,6 +130,14 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="171" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="172" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="6" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,12 +466,12 @@
   <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="81.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="82.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
     <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
     <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
   </cols>
@@ -4600,23 +4652,23 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>anio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>cobertura_neta</t>
         </is>
@@ -4712,23 +4764,23 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>anio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>desercion</t>
         </is>
@@ -4824,23 +4876,23 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>anio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="17" t="inlineStr">
         <is>
           <t>repitencia</t>
         </is>
@@ -4936,28 +4988,28 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="19" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="19" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="19" t="inlineStr">
         <is>
           <t>Cobertura neta</t>
         </is>
